--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF30BFA-2E8D-4336-A66D-BB923C30113C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A8EB77-53F7-419F-A927-59DEFAD2FB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -179,10 +168,6 @@
   </si>
   <si>
     <t>不好！啊啊啊啊！！！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>before</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -267,6 +252,10 @@
     <t>005治疗失败</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>sick</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -276,7 +265,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -290,7 +279,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -311,7 +300,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -465,7 +454,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -744,24 +733,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -784,28 +773,28 @@
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>39</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>40</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L1" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>37</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>38</v>
       </c>
       <c r="O1" s="19" t="s">
         <v>16</v>
@@ -819,7 +808,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
@@ -833,7 +822,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -917,14 +906,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -968,13 +957,13 @@
         <v>29</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>26</v>

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A8EB77-53F7-419F-A927-59DEFAD2FB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94E7F80-3594-4EA7-956A-558DFED097B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -140,10 +151,6 @@
   </si>
   <si>
     <t>咳咳咳，啊…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>楚恭王</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -256,6 +263,10 @@
     <t>sick</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>楚王</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -265,7 +276,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -279,7 +290,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -300,7 +311,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -454,7 +465,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -733,24 +744,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -773,28 +784,28 @@
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L1" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>36</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>37</v>
       </c>
       <c r="O1" s="19" t="s">
         <v>16</v>
@@ -808,7 +819,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>24</v>
@@ -822,7 +833,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -906,14 +917,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -954,16 +965,16 @@
         <v>25</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>26</v>
@@ -977,10 +988,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
@@ -988,7 +999,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1010,7 +1021,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1021,10 +1032,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
@@ -1032,7 +1043,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1054,7 +1065,7 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94E7F80-3594-4EA7-956A-558DFED097B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9079F7E-3DBA-48C6-B04A-4F63DFCF9C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -135,10 +135,6 @@
   </si>
   <si>
     <t>005_03</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -276,7 +272,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -290,7 +286,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -311,7 +307,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -465,7 +461,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -744,24 +740,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -784,28 +780,28 @@
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>35</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>36</v>
       </c>
       <c r="O1" s="19" t="s">
         <v>16</v>
@@ -819,10 +815,10 @@
         <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
@@ -833,7 +829,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -917,14 +913,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -962,22 +958,20 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -988,18 +982,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1016,12 +1008,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1032,18 +1022,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1060,12 +1048,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="8" t="s">
-        <v>23</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9079F7E-3DBA-48C6-B04A-4F63DFCF9C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDDFB71-B874-45F9-ADE4-120E7D135CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
   <si>
     <t>LineIndex</t>
   </si>
@@ -76,36 +62,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>night</t>
-  </si>
-  <si>
-    <t>night</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -138,10 +101,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>story_npc_failed_over</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>世子</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -174,36 +133,8 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>005_01</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -263,12 +194,100 @@
     <t>楚王</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,22 +346,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,20 +390,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -401,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -427,9 +462,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -445,19 +477,42 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,171 +794,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="23" customFormat="1">
+      <c r="A1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="R1" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="23" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="18"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="H7" s="18"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="18"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="18"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="18"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" s="26"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="15"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="18"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="18"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="18"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="18"/>
+      <c r="H20" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{C39CFDA6-A9FD-499E-9784-FAB11A54B253}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{BDAD2A32-70BC-4A7B-A11D-121BFAC14484}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{D61CE837-31BE-42F8-9ED2-A027825E9168}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{5A385088-D4FF-4FB9-8876-A79BA5E3105D}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{9597D05F-CDED-4194-9296-6FA63733EA32}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -926,28 +1008,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -955,23 +1037,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>24</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>42</v>
+        <v>18</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -979,19 +1061,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="12" t="s">
-        <v>28</v>
+      <c r="H3" s="11" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -999,19 +1081,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="12" t="s">
-        <v>29</v>
+      <c r="H4" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1019,19 +1101,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>43</v>
+        <v>5</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>27</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="12" t="s">
-        <v>30</v>
+      <c r="H5" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1039,19 +1121,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8"/>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1147,12 +1229,12 @@
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="12"/>
+      <c r="C16" s="11"/>
       <c r="D16" s="2"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="13"/>
+      <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1"/>
@@ -1162,17 +1244,17 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="13"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="12"/>
+      <c r="C18" s="11"/>
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="14"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3"/>

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDDFB71-B874-45F9-ADE4-120E7D135CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E02F9C3-D671-4FEA-8DDA-B297A4C9A516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="3570" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>SortIndex</t>
-  </si>
-  <si>
-    <t>night</t>
   </si>
   <si>
     <r>
@@ -281,6 +278,9 @@
   </si>
   <si>
     <t>failed</t>
+  </si>
+  <si>
+    <t>end_game</t>
   </si>
 </sst>
 </file>
@@ -804,7 +804,7 @@
     <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
@@ -815,58 +815,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="23" customFormat="1">
       <c r="A1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="O1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="P1" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="Q1" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="R1" s="21" t="s">
         <v>44</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>45</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>10</v>
@@ -875,12 +875,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="36">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -890,13 +890,13 @@
       <c r="H2" s="25"/>
       <c r="I2" s="24"/>
       <c r="J2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>46</v>
-      </c>
-      <c r="L2" s="25" t="s">
-        <v>12</v>
       </c>
       <c r="M2" s="24"/>
       <c r="N2" s="25"/>
@@ -1040,20 +1040,20 @@
         <v>5</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1064,16 +1064,16 @@
         <v>5</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1084,7 +1084,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>7</v>
@@ -1093,7 +1093,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1104,16 +1104,16 @@
         <v>5</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1124,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>7</v>
@@ -1133,7 +1133,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E02F9C3-D671-4FEA-8DDA-B297A4C9A516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63789162-4986-43E4-9333-560A73668FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="3570" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -280,7 +291,7 @@
     <t>failed</t>
   </si>
   <si>
-    <t>end_game</t>
+    <t>endgame</t>
   </si>
 </sst>
 </file>
@@ -291,7 +302,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -305,7 +316,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -326,7 +337,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -516,7 +527,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -795,25 +806,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>27</v>
       </c>
@@ -875,7 +886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1" ht="36">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
@@ -977,7 +988,7 @@
       <formula1>"≥,≤"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{D61CE837-31BE-42F8-9ED2-A027825E9168}">
-      <formula1>"clinic,night,end_game"</formula1>
+      <formula1>"clinic,night,endgame"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2" xr:uid="{5A385088-D4FF-4FB9-8876-A79BA5E3105D}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -995,14 +1006,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63789162-4986-43E4-9333-560A73668FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B9FE14-4CC0-4BBD-BF38-2819522A8509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13950" yWindow="3360" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -291,7 +280,7 @@
     <t>failed</t>
   </si>
   <si>
-    <t>endgame</t>
+    <t>gameover</t>
   </si>
 </sst>
 </file>
@@ -302,7 +291,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -316,7 +305,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -337,7 +326,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -527,7 +516,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -806,25 +795,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="23" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>27</v>
       </c>
@@ -886,7 +875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="23" customFormat="1">
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
@@ -987,14 +976,14 @@
     <dataValidation type="list" sqref="E2 G2" xr:uid="{BDAD2A32-70BC-4A7B-A11D-121BFAC14484}">
       <formula1>"≥,≤"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{D61CE837-31BE-42F8-9ED2-A027825E9168}">
-      <formula1>"clinic,night,endgame"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="S2" xr:uid="{5A385088-D4FF-4FB9-8876-A79BA5E3105D}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="K2" xr:uid="{9597D05F-CDED-4194-9296-6FA63733EA32}">
       <formula1>"cured,failed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{96EDB3E6-F67F-4BBC-9B3E-9409C2CD20D5}">
+      <formula1>"clinic,night,gameover,endgame"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1006,14 +995,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B9FE14-4CC0-4BBD-BF38-2819522A8509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C20292-DCEF-4455-9B60-4A8EC2367CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="3360" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20085" yWindow="5055" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
   <si>
     <t>LineIndex</t>
   </si>
@@ -282,6 +293,10 @@
   <si>
     <t>gameover</t>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
@@ -291,7 +306,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -305,7 +320,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -326,7 +341,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -436,7 +451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -514,9 +529,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -795,25 +813,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="23" customFormat="1">
+    <row r="1" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>27</v>
       </c>
@@ -875,7 +893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="23" customFormat="1">
+    <row r="2" spans="1:20" s="23" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
@@ -992,21 +1010,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1031,8 +1049,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1055,8 +1076,9 @@
       <c r="H2" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1075,8 +1097,9 @@
       <c r="H3" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1095,8 +1118,9 @@
       <c r="H4" s="11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1115,8 +1139,9 @@
       <c r="H5" s="11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1135,8 +1160,9 @@
       <c r="H6" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1145,8 +1171,9 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1155,8 +1182,9 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1165,8 +1193,9 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1175,8 +1204,9 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1185,8 +1215,9 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1195,8 +1226,9 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1205,8 +1237,9 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1215,8 +1248,9 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1225,8 +1259,9 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="11"/>
@@ -1235,8 +1270,9 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1245,8 +1281,9 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="12"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3"/>
       <c r="B18" s="1"/>
       <c r="C18" s="11"/>
@@ -1255,8 +1292,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1265,8 +1303,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1275,8 +1314,9 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1285,8 +1325,9 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1295,8 +1336,9 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1305,8 +1347,9 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1315,8 +1358,9 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1325,6 +1369,7 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/005_03治疗失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治疗失败.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C20292-DCEF-4455-9B60-4A8EC2367CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1110BCE5-DA46-490F-A4FA-F835AA52A6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20085" yWindow="5055" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -923,7 +923,7 @@
       <c r="Q2" s="25"/>
       <c r="R2" s="26"/>
       <c r="S2" s="26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" s="26"/>
     </row>
